--- a/artfynd/A 45016-2023 artfynd.xlsx
+++ b/artfynd/A 45016-2023 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122845686</v>
+        <v>122845395</v>
       </c>
       <c r="B2" t="n">
-        <v>78762</v>
+        <v>79847</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,21 +691,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>583168</v>
+        <v>583105</v>
       </c>
       <c r="R2" t="n">
-        <v>7041371</v>
+        <v>7041434</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -750,7 +750,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>15:12</t>
+          <t>15:04</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -760,7 +760,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>15:12</t>
+          <t>15:04</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -787,10 +787,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122845503</v>
+        <v>122845686</v>
       </c>
       <c r="B3" t="n">
-        <v>79843</v>
+        <v>78766</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -803,21 +803,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -827,10 +827,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>583129</v>
+        <v>583168</v>
       </c>
       <c r="R3" t="n">
-        <v>7041395</v>
+        <v>7041371</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -862,7 +862,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>15:08</t>
+          <t>15:12</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -872,7 +872,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>15:08</t>
+          <t>15:12</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -899,10 +899,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122845395</v>
+        <v>122845503</v>
       </c>
       <c r="B4" t="n">
-        <v>79843</v>
+        <v>79847</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -939,10 +939,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>583105</v>
+        <v>583129</v>
       </c>
       <c r="R4" t="n">
-        <v>7041434</v>
+        <v>7041395</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -974,7 +974,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>15:04</t>
+          <t>15:08</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -984,7 +984,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>15:04</t>
+          <t>15:08</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1014,7 +1014,7 @@
         <v>122845315</v>
       </c>
       <c r="B5" t="n">
-        <v>78762</v>
+        <v>78766</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>

--- a/artfynd/A 45016-2023 artfynd.xlsx
+++ b/artfynd/A 45016-2023 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122845395</v>
+        <v>122845315</v>
       </c>
       <c r="B2" t="n">
-        <v>79847</v>
+        <v>78766</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,21 +691,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>583105</v>
+        <v>583113</v>
       </c>
       <c r="R2" t="n">
-        <v>7041434</v>
+        <v>7041475</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -750,7 +750,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>15:04</t>
+          <t>15:01</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -760,7 +760,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>15:04</t>
+          <t>15:01</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -787,10 +787,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122845686</v>
+        <v>122845395</v>
       </c>
       <c r="B3" t="n">
-        <v>78766</v>
+        <v>79847</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -803,21 +803,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -827,10 +827,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>583168</v>
+        <v>583105</v>
       </c>
       <c r="R3" t="n">
-        <v>7041371</v>
+        <v>7041434</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -862,7 +862,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>15:12</t>
+          <t>15:04</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -872,7 +872,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>15:12</t>
+          <t>15:04</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -899,10 +899,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122845503</v>
+        <v>122845686</v>
       </c>
       <c r="B4" t="n">
-        <v>79847</v>
+        <v>78766</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -915,21 +915,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -939,10 +939,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>583129</v>
+        <v>583168</v>
       </c>
       <c r="R4" t="n">
-        <v>7041395</v>
+        <v>7041371</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -974,7 +974,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>15:08</t>
+          <t>15:12</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -984,7 +984,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>15:08</t>
+          <t>15:12</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1011,10 +1011,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122845315</v>
+        <v>122845503</v>
       </c>
       <c r="B5" t="n">
-        <v>78766</v>
+        <v>79847</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1027,21 +1027,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1051,10 +1051,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>583113</v>
+        <v>583129</v>
       </c>
       <c r="R5" t="n">
-        <v>7041475</v>
+        <v>7041395</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1086,7 +1086,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>15:01</t>
+          <t>15:08</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1096,7 +1096,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>15:01</t>
+          <t>15:08</t>
         </is>
       </c>
       <c r="AD5" t="b">

--- a/artfynd/A 45016-2023 artfynd.xlsx
+++ b/artfynd/A 45016-2023 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122845315</v>
+        <v>122845395</v>
       </c>
       <c r="B2" t="n">
-        <v>78766</v>
+        <v>79847</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,21 +691,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>583113</v>
+        <v>583105</v>
       </c>
       <c r="R2" t="n">
-        <v>7041475</v>
+        <v>7041434</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -750,7 +750,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>15:01</t>
+          <t>15:04</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -760,7 +760,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>15:01</t>
+          <t>15:04</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -787,10 +787,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122845395</v>
+        <v>122845686</v>
       </c>
       <c r="B3" t="n">
-        <v>79847</v>
+        <v>78766</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -803,21 +803,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -827,10 +827,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>583105</v>
+        <v>583168</v>
       </c>
       <c r="R3" t="n">
-        <v>7041434</v>
+        <v>7041371</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -862,7 +862,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>15:04</t>
+          <t>15:12</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -872,7 +872,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>15:04</t>
+          <t>15:12</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -899,10 +899,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122845686</v>
+        <v>122845503</v>
       </c>
       <c r="B4" t="n">
-        <v>78766</v>
+        <v>79847</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -915,21 +915,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -939,10 +939,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>583168</v>
+        <v>583129</v>
       </c>
       <c r="R4" t="n">
-        <v>7041371</v>
+        <v>7041395</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -974,7 +974,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>15:12</t>
+          <t>15:08</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -984,7 +984,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>15:12</t>
+          <t>15:08</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1011,10 +1011,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122845503</v>
+        <v>122845315</v>
       </c>
       <c r="B5" t="n">
-        <v>79847</v>
+        <v>78766</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1027,21 +1027,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1051,10 +1051,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>583129</v>
+        <v>583113</v>
       </c>
       <c r="R5" t="n">
-        <v>7041395</v>
+        <v>7041475</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1086,7 +1086,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>15:08</t>
+          <t>15:01</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1096,7 +1096,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>15:08</t>
+          <t>15:01</t>
         </is>
       </c>
       <c r="AD5" t="b">

--- a/artfynd/A 45016-2023 artfynd.xlsx
+++ b/artfynd/A 45016-2023 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122845395</v>
+        <v>122845686</v>
       </c>
       <c r="B2" t="n">
-        <v>79847</v>
+        <v>78766</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,21 +691,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>583105</v>
+        <v>583168</v>
       </c>
       <c r="R2" t="n">
-        <v>7041434</v>
+        <v>7041371</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -750,7 +750,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>15:04</t>
+          <t>15:12</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -760,7 +760,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>15:04</t>
+          <t>15:12</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -787,7 +787,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122845686</v>
+        <v>122845315</v>
       </c>
       <c r="B3" t="n">
         <v>78766</v>
@@ -827,10 +827,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>583168</v>
+        <v>583113</v>
       </c>
       <c r="R3" t="n">
-        <v>7041371</v>
+        <v>7041475</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -862,7 +862,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>15:12</t>
+          <t>15:01</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -872,7 +872,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>15:12</t>
+          <t>15:01</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -899,7 +899,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122845503</v>
+        <v>122845395</v>
       </c>
       <c r="B4" t="n">
         <v>79847</v>
@@ -939,10 +939,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>583129</v>
+        <v>583105</v>
       </c>
       <c r="R4" t="n">
-        <v>7041395</v>
+        <v>7041434</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -974,7 +974,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>15:08</t>
+          <t>15:04</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -984,7 +984,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>15:08</t>
+          <t>15:04</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1011,10 +1011,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122845315</v>
+        <v>122845503</v>
       </c>
       <c r="B5" t="n">
-        <v>78766</v>
+        <v>79847</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1027,21 +1027,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1051,10 +1051,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>583113</v>
+        <v>583129</v>
       </c>
       <c r="R5" t="n">
-        <v>7041475</v>
+        <v>7041395</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1086,7 +1086,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>15:01</t>
+          <t>15:08</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1096,7 +1096,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>15:01</t>
+          <t>15:08</t>
         </is>
       </c>
       <c r="AD5" t="b">

--- a/artfynd/A 45016-2023 artfynd.xlsx
+++ b/artfynd/A 45016-2023 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122845686</v>
+        <v>122845503</v>
       </c>
       <c r="B2" t="n">
-        <v>78766</v>
+        <v>79847</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,21 +691,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>583168</v>
+        <v>583129</v>
       </c>
       <c r="R2" t="n">
-        <v>7041371</v>
+        <v>7041395</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -750,7 +750,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>15:12</t>
+          <t>15:08</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -760,7 +760,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>15:12</t>
+          <t>15:08</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -899,10 +899,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122845395</v>
+        <v>122845686</v>
       </c>
       <c r="B4" t="n">
-        <v>79847</v>
+        <v>78766</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -915,21 +915,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -939,10 +939,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>583105</v>
+        <v>583168</v>
       </c>
       <c r="R4" t="n">
-        <v>7041434</v>
+        <v>7041371</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -974,7 +974,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>15:04</t>
+          <t>15:12</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -984,7 +984,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>15:04</t>
+          <t>15:12</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1011,7 +1011,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122845503</v>
+        <v>122845395</v>
       </c>
       <c r="B5" t="n">
         <v>79847</v>
@@ -1051,10 +1051,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>583129</v>
+        <v>583105</v>
       </c>
       <c r="R5" t="n">
-        <v>7041395</v>
+        <v>7041434</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1086,7 +1086,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>15:08</t>
+          <t>15:04</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1096,7 +1096,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>15:08</t>
+          <t>15:04</t>
         </is>
       </c>
       <c r="AD5" t="b">

--- a/artfynd/A 45016-2023 artfynd.xlsx
+++ b/artfynd/A 45016-2023 artfynd.xlsx
@@ -675,7 +675,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122845503</v>
+        <v>122845395</v>
       </c>
       <c r="B2" t="n">
         <v>79847</v>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>583129</v>
+        <v>583105</v>
       </c>
       <c r="R2" t="n">
-        <v>7041395</v>
+        <v>7041434</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -750,7 +750,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>15:08</t>
+          <t>15:04</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -760,7 +760,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>15:08</t>
+          <t>15:04</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -787,7 +787,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122845315</v>
+        <v>122845686</v>
       </c>
       <c r="B3" t="n">
         <v>78766</v>
@@ -827,10 +827,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>583113</v>
+        <v>583168</v>
       </c>
       <c r="R3" t="n">
-        <v>7041475</v>
+        <v>7041371</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -862,7 +862,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>15:01</t>
+          <t>15:12</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -872,7 +872,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>15:01</t>
+          <t>15:12</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -899,10 +899,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122845686</v>
+        <v>122845503</v>
       </c>
       <c r="B4" t="n">
-        <v>78766</v>
+        <v>79847</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -915,21 +915,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -939,10 +939,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>583168</v>
+        <v>583129</v>
       </c>
       <c r="R4" t="n">
-        <v>7041371</v>
+        <v>7041395</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -974,7 +974,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>15:12</t>
+          <t>15:08</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -984,7 +984,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>15:12</t>
+          <t>15:08</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1011,10 +1011,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122845395</v>
+        <v>122845315</v>
       </c>
       <c r="B5" t="n">
-        <v>79847</v>
+        <v>78766</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1027,21 +1027,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1051,10 +1051,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>583105</v>
+        <v>583113</v>
       </c>
       <c r="R5" t="n">
-        <v>7041434</v>
+        <v>7041475</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1086,7 +1086,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>15:04</t>
+          <t>15:01</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1096,7 +1096,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>15:04</t>
+          <t>15:01</t>
         </is>
       </c>
       <c r="AD5" t="b">

--- a/artfynd/A 45016-2023 artfynd.xlsx
+++ b/artfynd/A 45016-2023 artfynd.xlsx
@@ -675,7 +675,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122845395</v>
+        <v>122845503</v>
       </c>
       <c r="B2" t="n">
         <v>79847</v>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>583105</v>
+        <v>583129</v>
       </c>
       <c r="R2" t="n">
-        <v>7041434</v>
+        <v>7041395</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -750,7 +750,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>15:04</t>
+          <t>15:08</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -760,7 +760,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>15:04</t>
+          <t>15:08</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -787,10 +787,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122845686</v>
+        <v>122845395</v>
       </c>
       <c r="B3" t="n">
-        <v>78766</v>
+        <v>79847</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -803,21 +803,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -827,10 +827,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>583168</v>
+        <v>583105</v>
       </c>
       <c r="R3" t="n">
-        <v>7041371</v>
+        <v>7041434</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -862,7 +862,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>15:12</t>
+          <t>15:04</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -872,7 +872,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>15:12</t>
+          <t>15:04</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -899,10 +899,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122845503</v>
+        <v>122845315</v>
       </c>
       <c r="B4" t="n">
-        <v>79847</v>
+        <v>78766</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -915,21 +915,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -939,10 +939,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>583129</v>
+        <v>583113</v>
       </c>
       <c r="R4" t="n">
-        <v>7041395</v>
+        <v>7041475</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -974,7 +974,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>15:08</t>
+          <t>15:01</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -984,7 +984,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>15:08</t>
+          <t>15:01</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1011,7 +1011,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122845315</v>
+        <v>122845686</v>
       </c>
       <c r="B5" t="n">
         <v>78766</v>
@@ -1051,10 +1051,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>583113</v>
+        <v>583168</v>
       </c>
       <c r="R5" t="n">
-        <v>7041475</v>
+        <v>7041371</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1086,7 +1086,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>15:01</t>
+          <t>15:12</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1096,7 +1096,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>15:01</t>
+          <t>15:12</t>
         </is>
       </c>
       <c r="AD5" t="b">

--- a/artfynd/A 45016-2023 artfynd.xlsx
+++ b/artfynd/A 45016-2023 artfynd.xlsx
@@ -675,7 +675,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122845503</v>
+        <v>122845395</v>
       </c>
       <c r="B2" t="n">
         <v>79847</v>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>583129</v>
+        <v>583105</v>
       </c>
       <c r="R2" t="n">
-        <v>7041395</v>
+        <v>7041434</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -750,7 +750,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>15:08</t>
+          <t>15:04</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -760,7 +760,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>15:08</t>
+          <t>15:04</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -787,10 +787,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122845395</v>
+        <v>122845315</v>
       </c>
       <c r="B3" t="n">
-        <v>79847</v>
+        <v>78766</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -803,21 +803,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -827,10 +827,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>583105</v>
+        <v>583113</v>
       </c>
       <c r="R3" t="n">
-        <v>7041434</v>
+        <v>7041475</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -862,7 +862,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>15:04</t>
+          <t>15:01</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -872,7 +872,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>15:04</t>
+          <t>15:01</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -899,10 +899,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122845315</v>
+        <v>122845503</v>
       </c>
       <c r="B4" t="n">
-        <v>78766</v>
+        <v>79847</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -915,21 +915,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -939,10 +939,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>583113</v>
+        <v>583129</v>
       </c>
       <c r="R4" t="n">
-        <v>7041475</v>
+        <v>7041395</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -974,7 +974,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>15:01</t>
+          <t>15:08</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -984,7 +984,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>15:01</t>
+          <t>15:08</t>
         </is>
       </c>
       <c r="AD4" t="b">

--- a/artfynd/A 45016-2023 artfynd.xlsx
+++ b/artfynd/A 45016-2023 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122845395</v>
+        <v>122845315</v>
       </c>
       <c r="B2" t="n">
-        <v>79847</v>
+        <v>78769</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,21 +691,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>583105</v>
+        <v>583113</v>
       </c>
       <c r="R2" t="n">
-        <v>7041434</v>
+        <v>7041475</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -750,7 +750,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>15:04</t>
+          <t>15:01</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -760,7 +760,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>15:04</t>
+          <t>15:01</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -787,10 +787,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122845315</v>
+        <v>122845503</v>
       </c>
       <c r="B3" t="n">
-        <v>78766</v>
+        <v>79850</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -803,21 +803,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -827,10 +827,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>583113</v>
+        <v>583129</v>
       </c>
       <c r="R3" t="n">
-        <v>7041475</v>
+        <v>7041395</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -862,7 +862,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>15:01</t>
+          <t>15:08</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -872,7 +872,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>15:01</t>
+          <t>15:08</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -899,10 +899,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122845503</v>
+        <v>122845686</v>
       </c>
       <c r="B4" t="n">
-        <v>79847</v>
+        <v>78769</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -915,21 +915,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -939,10 +939,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>583129</v>
+        <v>583168</v>
       </c>
       <c r="R4" t="n">
-        <v>7041395</v>
+        <v>7041371</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -974,7 +974,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>15:08</t>
+          <t>15:12</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -984,7 +984,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>15:08</t>
+          <t>15:12</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1011,10 +1011,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122845686</v>
+        <v>122845395</v>
       </c>
       <c r="B5" t="n">
-        <v>78766</v>
+        <v>79850</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1027,21 +1027,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1051,10 +1051,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>583168</v>
+        <v>583105</v>
       </c>
       <c r="R5" t="n">
-        <v>7041371</v>
+        <v>7041434</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1086,7 +1086,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>15:12</t>
+          <t>15:04</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1096,7 +1096,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>15:12</t>
+          <t>15:04</t>
         </is>
       </c>
       <c r="AD5" t="b">

--- a/artfynd/A 45016-2023 artfynd.xlsx
+++ b/artfynd/A 45016-2023 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122845315</v>
+        <v>122845395</v>
       </c>
       <c r="B2" t="n">
-        <v>78769</v>
+        <v>79852</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,21 +691,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>583113</v>
+        <v>583105</v>
       </c>
       <c r="R2" t="n">
-        <v>7041475</v>
+        <v>7041434</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -750,7 +750,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>15:01</t>
+          <t>15:04</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -760,7 +760,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>15:01</t>
+          <t>15:04</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -787,10 +787,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122845503</v>
+        <v>122845686</v>
       </c>
       <c r="B3" t="n">
-        <v>79850</v>
+        <v>78771</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -803,21 +803,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -827,10 +827,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>583129</v>
+        <v>583168</v>
       </c>
       <c r="R3" t="n">
-        <v>7041395</v>
+        <v>7041371</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -862,7 +862,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>15:08</t>
+          <t>15:12</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -872,7 +872,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>15:08</t>
+          <t>15:12</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -899,10 +899,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122845686</v>
+        <v>122845315</v>
       </c>
       <c r="B4" t="n">
-        <v>78769</v>
+        <v>78771</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -939,10 +939,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>583168</v>
+        <v>583113</v>
       </c>
       <c r="R4" t="n">
-        <v>7041371</v>
+        <v>7041475</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -974,7 +974,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>15:12</t>
+          <t>15:01</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -984,7 +984,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>15:12</t>
+          <t>15:01</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1011,10 +1011,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122845395</v>
+        <v>122845503</v>
       </c>
       <c r="B5" t="n">
-        <v>79850</v>
+        <v>79852</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1051,10 +1051,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>583105</v>
+        <v>583129</v>
       </c>
       <c r="R5" t="n">
-        <v>7041434</v>
+        <v>7041395</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1086,7 +1086,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>15:04</t>
+          <t>15:08</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1096,7 +1096,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>15:04</t>
+          <t>15:08</t>
         </is>
       </c>
       <c r="AD5" t="b">

--- a/artfynd/A 45016-2023 artfynd.xlsx
+++ b/artfynd/A 45016-2023 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122845395</v>
+        <v>122845503</v>
       </c>
       <c r="B2" t="n">
-        <v>79852</v>
+        <v>79853</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>583105</v>
+        <v>583129</v>
       </c>
       <c r="R2" t="n">
-        <v>7041434</v>
+        <v>7041395</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -750,7 +750,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>15:04</t>
+          <t>15:08</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -760,7 +760,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>15:04</t>
+          <t>15:08</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -790,7 +790,7 @@
         <v>122845686</v>
       </c>
       <c r="B3" t="n">
-        <v>78771</v>
+        <v>78772</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -899,10 +899,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122845315</v>
+        <v>122845395</v>
       </c>
       <c r="B4" t="n">
-        <v>78771</v>
+        <v>79853</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -915,21 +915,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -939,10 +939,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>583113</v>
+        <v>583105</v>
       </c>
       <c r="R4" t="n">
-        <v>7041475</v>
+        <v>7041434</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -974,7 +974,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>15:01</t>
+          <t>15:04</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -984,7 +984,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>15:01</t>
+          <t>15:04</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1011,10 +1011,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122845503</v>
+        <v>122845315</v>
       </c>
       <c r="B5" t="n">
-        <v>79852</v>
+        <v>78772</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1027,21 +1027,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1051,10 +1051,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>583129</v>
+        <v>583113</v>
       </c>
       <c r="R5" t="n">
-        <v>7041395</v>
+        <v>7041475</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1086,7 +1086,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>15:08</t>
+          <t>15:01</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1096,7 +1096,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>15:08</t>
+          <t>15:01</t>
         </is>
       </c>
       <c r="AD5" t="b">

--- a/artfynd/A 45016-2023 artfynd.xlsx
+++ b/artfynd/A 45016-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY5"/>
+  <dimension ref="A1:AY6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,37 +675,32 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122845395</v>
+        <v>122845315</v>
       </c>
       <c r="B2" t="n">
-        <v>79856</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>583105</v>
+        <v>583113</v>
       </c>
       <c r="R2" t="n">
-        <v>7041434</v>
+        <v>7041475</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -750,7 +745,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>15:04</t>
+          <t>15:01</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -760,7 +755,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>15:04</t>
+          <t>15:01</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -790,16 +785,11 @@
         <v>122845686</v>
       </c>
       <c r="B3" t="n">
-        <v>78775</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E3" t="n">
@@ -899,15 +889,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122845315</v>
+        <v>122845395</v>
       </c>
       <c r="B4" t="n">
-        <v>78775</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80432</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -915,21 +900,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -939,10 +924,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>583113</v>
+        <v>583105</v>
       </c>
       <c r="R4" t="n">
-        <v>7041475</v>
+        <v>7041434</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -974,7 +959,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>15:01</t>
+          <t>15:04</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -984,7 +969,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>15:01</t>
+          <t>15:04</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1014,12 +999,7 @@
         <v>122845503</v>
       </c>
       <c r="B5" t="n">
-        <v>79856</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80432</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1120,6 +1100,118 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>123270630</v>
+      </c>
+      <c r="B6" t="n">
+        <v>57141</v>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>100138</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Tjäder</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Tetrao urogallus</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>Tosklokklippen, Tosklokklippen, Ång</t>
+        </is>
+      </c>
+      <c r="Q6" t="n">
+        <v>583098</v>
+      </c>
+      <c r="R6" t="n">
+        <v>7041550</v>
+      </c>
+      <c r="S6" t="n">
+        <v>10</v>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>Ådals-Liden</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>2025-03-17</t>
+        </is>
+      </c>
+      <c r="Z6" t="inlineStr">
+        <is>
+          <t>13:30</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>2025-03-17</t>
+        </is>
+      </c>
+      <c r="AB6" t="inlineStr">
+        <is>
+          <t>13:30</t>
+        </is>
+      </c>
+      <c r="AD6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT6" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>Kim Hultgren</t>
+        </is>
+      </c>
+      <c r="AX6" t="inlineStr">
+        <is>
+          <t>Kim Hultgren</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 45016-2023 artfynd.xlsx
+++ b/artfynd/A 45016-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY6"/>
+  <dimension ref="A1:AZ6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -779,6 +784,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122845315</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -886,6 +896,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122845686</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -993,6 +1008,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122845395</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1100,6 +1120,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122845503</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1212,8 +1237,20 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123270630</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>